--- a/Team4_BOM_v1.xlsx
+++ b/Team4_BOM_v1.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B1A0847-3B42-4922-99AD-9C5456DBB3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60709675-C06C-4C11-9489-7BF96CB71CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47910" yWindow="-2350" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Itemized expenses" sheetId="2" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>Item</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>Battery Pack</t>
-  </si>
-  <si>
-    <t>DC Motor</t>
   </si>
   <si>
     <t>Fly Wheel</t>
@@ -144,6 +141,24 @@
   </si>
   <si>
     <t>https://www.amazon.com/Ferwooh-Protoboard-Breadboards-Breadboard-Electronic/dp/B0CZ6W18F6?dib=eyJ2IjoiMSJ9.hZ7yUlqIa0lR5GczvXnkXXRkct3_5aQwM13_NnqxYdWNbnpS2dY9WPIgSeb6-rpPEJcG9WB-KjlE51xRiUVdTZLSnqCPGqGrLIuTBPsUXruDgx5sbPV5fl6Bfclzp53MPIWCZtQ2KUbuzj-DyeXDRlsgvUU42EsXcL0h90DZIPnXiZTmJsZEROvv70xDJaRbHvpyaJkhLfH8KOCTQ20UPjC2mkwTb6tuwN4uNDaFS_E.UwTda-DkAShUyBvcAmocGrK2EzXhMQmItb_AAQ2dud4&amp;dib_tag=se&amp;keywords=perfboard&amp;qid=1762212236&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t>ZYTD520 DC Motor</t>
+  </si>
+  <si>
+    <t>LM8UU Linear Bearings</t>
+  </si>
+  <si>
+    <t>6 8mm Bearings</t>
+  </si>
+  <si>
+    <t>12 Wiffleballs</t>
+  </si>
+  <si>
+    <t>tbd</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B07HYXD3Q8?psc=1&amp;smid=ATVPDKIKX0DER&amp;ref_=chk_typ_quicklook_titleToDp</t>
   </si>
 </sst>
 </file>
@@ -947,8 +962,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>280394</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Category" descr="Select an item in the slicer to filter the list">
@@ -971,7 +986,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -1093,16 +1108,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Data" displayName="Data" ref="B5:F15" totalsRowCount="1" headerRowCellStyle="Heading 2">
-  <autoFilter ref="B5:F14" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Data" displayName="Data" ref="B5:F18" totalsRowCount="1" headerRowCellStyle="Heading 2">
+  <autoFilter ref="B5:F17" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:E14">
-    <sortCondition descending="1" ref="D5:D14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:E16">
+    <sortCondition descending="1" ref="D5:D16"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Item" totalsRowLabel="Total" totalsRowDxfId="1"/>
@@ -1351,7 +1366,7 @@
     <tabColor theme="5"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:F15"/>
+  <dimension ref="B1:F18"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
@@ -1364,7 +1379,7 @@
   <sheetData>
     <row r="1" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>9</v>
@@ -1372,10 +1387,10 @@
     </row>
     <row r="2" spans="2:6" ht="73.150000000000006" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1398,11 +1413,11 @@
       </c>
       <c r="C4" s="6">
         <f>SUM(Data[Amount])</f>
-        <v>38.81</v>
+        <v>39.940000000000005</v>
       </c>
       <c r="D4" s="6">
         <f>B4-C4</f>
-        <v>111.19</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -1419,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
@@ -1475,7 +1490,7 @@
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -1492,67 +1507,67 @@
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="8">
-        <v>12.86</v>
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="8">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="8">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
       <c r="F12" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="8">
-        <v>4.99</v>
+        <v>5.97</v>
       </c>
       <c r="F13" s="11" t="b">
         <v>0</v>
@@ -1560,29 +1575,83 @@
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" s="8">
-        <v>0</v>
+        <v>14.99</v>
       </c>
       <c r="F14" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="12" t="s">
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="8">
+        <v>4.99</v>
+      </c>
+      <c r="F15" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="8">
+        <v>6</v>
+      </c>
+      <c r="F17" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E18" s="7">
         <f>SUBTOTAL(109,Data[Amount])</f>
-        <v>38.81</v>
+        <v>39.940000000000005</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E6:F14">
+  <conditionalFormatting sqref="E6:F17">
     <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
@@ -1638,7 +1707,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E6:F14</xm:sqref>
+          <xm:sqref>E6:F17</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -1688,12 +1757,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1997,29 +2077,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B20188-3F1D-48BB-98B3-500715844889}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DB4BF5E-B69C-4F09-8DD4-7CE1F2025B9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2046,13 +2119,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DB4BF5E-B69C-4F09-8DD4-7CE1F2025B9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B20188-3F1D-48BB-98B3-500715844889}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
